--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C212CC08-2393-43EC-9D91-7C0A55B19E08}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE7F5E37-DFDA-43EE-9939-DC9BCD564FE3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>bored</t>
+  </si>
+  <si>
+    <t>eff3rcvbnm,.</t>
   </si>
 </sst>
 </file>
@@ -298,10 +301,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -885,7 +884,9 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
-      <c r="B9" s="9"/>
+      <c r="B9" s="9" t="s">
+        <v>30</v>
+      </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE7F5E37-DFDA-43EE-9939-DC9BCD564FE3}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8BD1E82-F709-4807-98F4-1CF9473B5DB2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -128,7 +128,7 @@
     <t>bored</t>
   </si>
   <si>
-    <t>eff3rcvbnm,.</t>
+    <t>good</t>
   </si>
 </sst>
 </file>
@@ -301,6 +301,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -883,28 +887,50 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9" t="s">
+      <c r="A9" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B9" s="9">
+        <v>420</v>
+      </c>
+      <c r="C9" s="9">
+        <v>35</v>
+      </c>
+      <c r="D9" s="9">
+        <v>120</v>
+      </c>
+      <c r="E9" s="9">
+        <v>60</v>
+      </c>
+      <c r="F9" s="9">
+        <v>350</v>
+      </c>
+      <c r="G9" s="9">
+        <v>7</v>
+      </c>
+      <c r="H9" s="9">
+        <v>180</v>
+      </c>
+      <c r="I9" s="10">
+        <f t="shared" si="0"/>
+        <v>1165</v>
+      </c>
+      <c r="J9" s="10">
+        <f t="shared" si="1"/>
+        <v>275</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8BD1E82-F709-4807-98F4-1CF9473B5DB2}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EBF61BC-8AF2-415C-B8E0-8B7830E74508}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -129,6 +129,15 @@
   </si>
   <si>
     <t>good</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -933,47 +942,93 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10" t="str">
+      <c r="A10" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B10" s="9">
+        <v>420</v>
+      </c>
+      <c r="C10" s="9">
+        <v>45</v>
+      </c>
+      <c r="D10" s="9">
+        <v>90</v>
+      </c>
+      <c r="E10" s="9">
+        <v>45</v>
+      </c>
+      <c r="F10" s="9">
+        <v>200</v>
+      </c>
+      <c r="G10" s="9">
+        <v>4</v>
+      </c>
+      <c r="H10" s="9">
+        <v>150</v>
+      </c>
+      <c r="I10" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="10" t="str">
+        <v>950</v>
+      </c>
+      <c r="J10" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="12"/>
+        <v>490</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10" t="str">
+      <c r="A11" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B11" s="9">
+        <v>420</v>
+      </c>
+      <c r="C11" s="9">
+        <v>30</v>
+      </c>
+      <c r="D11" s="9">
+        <v>60</v>
+      </c>
+      <c r="E11" s="9">
+        <v>30</v>
+      </c>
+      <c r="F11" s="9">
+        <v>350</v>
+      </c>
+      <c r="G11" s="9">
+        <v>7</v>
+      </c>
+      <c r="H11" s="9">
+        <v>120</v>
+      </c>
+      <c r="I11" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="10" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J11" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
+        <v>430</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>33</v>
+      </c>
       <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EBF61BC-8AF2-415C-B8E0-8B7830E74508}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A6DC0E0-A03D-4C7A-B2CB-73923A9ECBAB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -138,6 +138,12 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>enjoying  raksha  bandhan</t>
   </si>
 </sst>
 </file>
@@ -1031,27 +1037,51 @@
       </c>
       <c r="N11" s="12"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10" t="str">
+    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B12" s="9">
+        <v>420</v>
+      </c>
+      <c r="C12" s="9">
+        <v>30</v>
+      </c>
+      <c r="D12" s="9">
+        <v>60</v>
+      </c>
+      <c r="E12" s="9">
+        <v>45</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>300</v>
+      </c>
+      <c r="I12" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="10" t="str">
+        <v>855</v>
+      </c>
+      <c r="J12" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="12"/>
+        <v>585</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A6DC0E0-A03D-4C7A-B2CB-73923A9ECBAB}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29CA1BDA-6E0E-4B6A-9801-4E170AD590A2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>enjoying  raksha  bandhan</t>
+  </si>
+  <si>
+    <t>playing cricket in weak</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1042,7 @@
     </row>
     <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B12" s="9">
         <v>420</v>
@@ -1084,26 +1087,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10" t="str">
+      <c r="A13" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B13" s="9">
+        <v>480</v>
+      </c>
+      <c r="C13" s="9">
+        <v>60</v>
+      </c>
+      <c r="D13" s="9">
+        <v>90</v>
+      </c>
+      <c r="E13" s="9">
+        <v>30</v>
+      </c>
+      <c r="F13" s="9">
+        <v>0</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>90</v>
+      </c>
+      <c r="I13" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="10" t="str">
+        <v>750</v>
+      </c>
+      <c r="J13" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="12"/>
+        <v>690</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29CA1BDA-6E0E-4B6A-9801-4E170AD590A2}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86CA6E69-6CE5-4DAA-857F-23E767DEE64A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -147,6 +147,12 @@
   </si>
   <si>
     <t>playing cricket in weak</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>enjoy time with family</t>
   </si>
 </sst>
 </file>
@@ -1133,26 +1139,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10" t="str">
+      <c r="A14" s="8">
+        <v>46264</v>
+      </c>
+      <c r="B14" s="9">
+        <v>420</v>
+      </c>
+      <c r="C14" s="9">
+        <v>60</v>
+      </c>
+      <c r="D14" s="9">
+        <v>45</v>
+      </c>
+      <c r="E14" s="9">
+        <v>30</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>180</v>
+      </c>
+      <c r="I14" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="10" t="str">
+        <v>735</v>
+      </c>
+      <c r="J14" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="12"/>
+        <v>705</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86CA6E69-6CE5-4DAA-857F-23E767DEE64A}"/>
+  <xr:revisionPtr revIDLastSave="170" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E0D949C-8472-4547-90F3-CA9A97B04CCC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -153,6 +153,9 @@
   </si>
   <si>
     <t>enjoy time with family</t>
+  </si>
+  <si>
+    <t>normal</t>
   </si>
 </sst>
 </file>
@@ -1185,26 +1188,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10" t="str">
+      <c r="A15" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B15" s="9">
+        <v>420</v>
+      </c>
+      <c r="C15" s="9">
+        <v>40</v>
+      </c>
+      <c r="D15" s="9">
+        <v>40</v>
+      </c>
+      <c r="E15" s="9">
+        <v>30</v>
+      </c>
+      <c r="F15" s="9">
+        <v>350</v>
+      </c>
+      <c r="G15" s="9">
+        <v>7</v>
+      </c>
+      <c r="H15" s="9">
+        <v>180</v>
+      </c>
+      <c r="I15" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="10" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J15" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="12"/>
+        <v>380</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="170" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E0D949C-8472-4547-90F3-CA9A97B04CCC}"/>
+  <xr:revisionPtr revIDLastSave="182" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9852BE1C-4B59-4D72-9F0F-2D47934A851B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>normal</t>
+  </si>
+  <si>
+    <t>travelling</t>
   </si>
 </sst>
 </file>
@@ -1234,26 +1237,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10" t="str">
+      <c r="A16" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B16" s="9">
+        <v>420</v>
+      </c>
+      <c r="C16" s="9">
+        <v>40</v>
+      </c>
+      <c r="D16" s="9">
+        <v>30</v>
+      </c>
+      <c r="E16" s="9">
+        <v>40</v>
+      </c>
+      <c r="F16" s="9">
+        <v>200</v>
+      </c>
+      <c r="G16" s="9">
+        <v>4</v>
+      </c>
+      <c r="H16" s="9">
+        <v>220</v>
+      </c>
+      <c r="I16" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="10" t="str">
+        <v>950</v>
+      </c>
+      <c r="J16" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="12"/>
+        <v>490</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9852BE1C-4B59-4D72-9F0F-2D47934A851B}"/>
+  <xr:revisionPtr revIDLastSave="194" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FF6BFD8-B0D6-46E0-84A3-9982065001F0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="41">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -1283,26 +1283,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10" t="str">
+      <c r="A17" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B17" s="9">
+        <v>420</v>
+      </c>
+      <c r="C17" s="9">
+        <v>60</v>
+      </c>
+      <c r="D17" s="9">
+        <v>50</v>
+      </c>
+      <c r="E17" s="9">
+        <v>45</v>
+      </c>
+      <c r="F17" s="9">
+        <v>350</v>
+      </c>
+      <c r="G17" s="9">
+        <v>7</v>
+      </c>
+      <c r="H17" s="9">
+        <v>120</v>
+      </c>
+      <c r="I17" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="10" t="str">
+        <v>1045</v>
+      </c>
+      <c r="J17" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="12"/>
+        <v>395</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="194" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FF6BFD8-B0D6-46E0-84A3-9982065001F0}"/>
+  <xr:revisionPtr revIDLastSave="208" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{553F8E2B-EAC6-4541-9106-88A2665679F1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="42">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t>travelling</t>
+  </si>
+  <si>
+    <t>not well</t>
   </si>
 </sst>
 </file>
@@ -1329,26 +1332,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10" t="str">
+      <c r="A18" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B18" s="9">
+        <v>420</v>
+      </c>
+      <c r="C18" s="9">
+        <v>45</v>
+      </c>
+      <c r="D18" s="9">
+        <v>45</v>
+      </c>
+      <c r="E18" s="9">
+        <v>30</v>
+      </c>
+      <c r="F18" s="9">
+        <v>300</v>
+      </c>
+      <c r="G18" s="9">
+        <v>6</v>
+      </c>
+      <c r="H18" s="9">
+        <v>150</v>
+      </c>
+      <c r="I18" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="10" t="str">
+        <v>990</v>
+      </c>
+      <c r="J18" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="12"/>
+        <v>450</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="208" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{553F8E2B-EAC6-4541-9106-88A2665679F1}"/>
+  <xr:revisionPtr revIDLastSave="221" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87A04EC6-21B0-44F5-96DE-01B53970D1EB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -162,6 +162,12 @@
   </si>
   <si>
     <t>not well</t>
+  </si>
+  <si>
+    <t>2026-09-05-</t>
+  </si>
+  <si>
+    <t>playing cricket</t>
   </si>
 </sst>
 </file>
@@ -1378,26 +1384,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10" t="str">
+      <c r="A19" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="9">
+        <v>420</v>
+      </c>
+      <c r="C19" s="9">
+        <v>60</v>
+      </c>
+      <c r="D19" s="9">
+        <v>120</v>
+      </c>
+      <c r="E19" s="9">
+        <v>150</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9">
+        <v>200</v>
+      </c>
+      <c r="I19" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="10" t="str">
+        <v>950</v>
+      </c>
+      <c r="J19" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="12"/>
+        <v>490</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="221" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87A04EC6-21B0-44F5-96DE-01B53970D1EB}"/>
+  <xr:revisionPtr revIDLastSave="234" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D64F9150-9B91-46D4-B25E-BACE0E507C2B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="44">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -164,10 +164,10 @@
     <t>not well</t>
   </si>
   <si>
-    <t>2026-09-05-</t>
+    <t>playing cricket</t>
   </si>
   <si>
-    <t>playing cricket</t>
+    <t>relaxed</t>
   </si>
 </sst>
 </file>
@@ -1384,8 +1384,8 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
-        <v>42</v>
+      <c r="A19" s="8">
+        <v>46270</v>
       </c>
       <c r="B19" s="9">
         <v>420</v>
@@ -1426,30 +1426,54 @@
         <v>31</v>
       </c>
       <c r="N19" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B20" s="9">
+        <v>480</v>
+      </c>
+      <c r="C20" s="9">
+        <v>80</v>
+      </c>
+      <c r="D20" s="9">
+        <v>100</v>
+      </c>
+      <c r="E20" s="9">
+        <v>120</v>
+      </c>
+      <c r="F20" s="9">
+        <v>0</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>180</v>
+      </c>
+      <c r="I20" s="10">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J20" s="10">
+        <f t="shared" si="1"/>
+        <v>480</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N20" s="12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="234" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D64F9150-9B91-46D4-B25E-BACE0E507C2B}"/>
+  <xr:revisionPtr revIDLastSave="246" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92283CEE-E849-45CB-8398-42CE4BE50210}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="44">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -1476,26 +1476,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="10" t="str">
+      <c r="A21" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B21" s="9">
+        <v>420</v>
+      </c>
+      <c r="C21" s="9">
+        <v>60</v>
+      </c>
+      <c r="D21" s="9">
+        <v>60</v>
+      </c>
+      <c r="E21" s="9">
+        <v>45</v>
+      </c>
+      <c r="F21" s="9">
+        <v>150</v>
+      </c>
+      <c r="G21" s="9">
+        <v>3</v>
+      </c>
+      <c r="H21" s="9">
+        <v>180</v>
+      </c>
+      <c r="I21" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="10" t="str">
+        <v>915</v>
+      </c>
+      <c r="J21" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="12"/>
+        <v>525</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="246" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92283CEE-E849-45CB-8398-42CE4BE50210}"/>
+  <xr:revisionPtr revIDLastSave="258" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA35EAD3-3D57-4A42-87EA-16BA58DD6419}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="45">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>relaxed</t>
+  </si>
+  <si>
+    <t>lot of classes</t>
   </si>
 </sst>
 </file>
@@ -1522,26 +1525,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="10" t="str">
+      <c r="A22" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B22" s="9">
+        <v>420</v>
+      </c>
+      <c r="C22" s="9">
+        <v>45</v>
+      </c>
+      <c r="D22" s="9">
+        <v>50</v>
+      </c>
+      <c r="E22" s="9">
+        <v>45</v>
+      </c>
+      <c r="F22" s="9">
+        <v>350</v>
+      </c>
+      <c r="G22" s="9">
+        <v>7</v>
+      </c>
+      <c r="H22" s="9">
+        <v>120</v>
+      </c>
+      <c r="I22" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="10" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J22" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="12"/>
+        <v>410</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="258" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA35EAD3-3D57-4A42-87EA-16BA58DD6419}"/>
+  <xr:revisionPtr revIDLastSave="270" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28D37138-18F2-413A-96EE-8EE2AEEC1F19}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="45">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -1571,26 +1571,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="10" t="str">
+      <c r="A23" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B23" s="9">
+        <v>420</v>
+      </c>
+      <c r="C23" s="9">
+        <v>50</v>
+      </c>
+      <c r="D23" s="9">
+        <v>40</v>
+      </c>
+      <c r="E23" s="9">
+        <v>30</v>
+      </c>
+      <c r="F23" s="9">
+        <v>200</v>
+      </c>
+      <c r="G23" s="9">
+        <v>4</v>
+      </c>
+      <c r="H23" s="9">
+        <v>150</v>
+      </c>
+      <c r="I23" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="10" t="str">
+        <v>890</v>
+      </c>
+      <c r="J23" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="12"/>
+        <v>550</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="270" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28D37138-18F2-413A-96EE-8EE2AEEC1F19}"/>
+  <xr:revisionPtr revIDLastSave="282" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E578916-A3B9-4605-B23F-B2DA6D704752}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="45">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -1617,26 +1617,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="10" t="str">
+      <c r="A24" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B24" s="9">
+        <v>420</v>
+      </c>
+      <c r="C24" s="9">
+        <v>40</v>
+      </c>
+      <c r="D24" s="9">
+        <v>30</v>
+      </c>
+      <c r="E24" s="9">
+        <v>40</v>
+      </c>
+      <c r="F24" s="9">
+        <v>350</v>
+      </c>
+      <c r="G24" s="9">
+        <v>7</v>
+      </c>
+      <c r="H24" s="9">
+        <v>180</v>
+      </c>
+      <c r="I24" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="10" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J24" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="12"/>
+        <v>380</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="282" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E578916-A3B9-4605-B23F-B2DA6D704752}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8A9BA32-009D-4F4D-A4F8-5B3C1BA8A03D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="46">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -171,6 +171,9 @@
   </si>
   <si>
     <t>lot of classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tired </t>
   </si>
 </sst>
 </file>
@@ -1663,26 +1666,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="10" t="str">
+      <c r="A25" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B25" s="9">
+        <v>420</v>
+      </c>
+      <c r="C25" s="9">
+        <v>45</v>
+      </c>
+      <c r="D25" s="9">
+        <v>90</v>
+      </c>
+      <c r="E25" s="9">
+        <v>40</v>
+      </c>
+      <c r="F25" s="9">
+        <v>300</v>
+      </c>
+      <c r="G25" s="9">
+        <v>6</v>
+      </c>
+      <c r="H25" s="9">
+        <v>200</v>
+      </c>
+      <c r="I25" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="10" t="str">
+        <v>1095</v>
+      </c>
+      <c r="J25" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="12"/>
+        <v>345</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="295" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8A9BA32-009D-4F4D-A4F8-5B3C1BA8A03D}"/>
+  <xr:revisionPtr revIDLastSave="307" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{739E24B5-3A86-4C5C-A765-168A93597CE2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="47">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -174,6 +174,9 @@
   </si>
   <si>
     <t xml:space="preserve">tired </t>
+  </si>
+  <si>
+    <t>out of station</t>
   </si>
 </sst>
 </file>
@@ -1712,26 +1715,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10" t="str">
+      <c r="A26" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B26" s="9">
+        <v>480</v>
+      </c>
+      <c r="C26" s="9">
+        <v>0</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>300</v>
+      </c>
+      <c r="I26" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="10" t="str">
+        <v>780</v>
+      </c>
+      <c r="J26" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="12"/>
+        <v>660</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="307" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{739E24B5-3A86-4C5C-A765-168A93597CE2}"/>
+  <xr:revisionPtr revIDLastSave="319" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35EB406E-B796-4869-B7ED-61E931538ED9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="48">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t>out of station</t>
+  </si>
+  <si>
+    <t>return home &amp; light revision</t>
   </si>
 </sst>
 </file>
@@ -1760,27 +1763,51 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="10" t="str">
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B27" s="9">
+        <v>500</v>
+      </c>
+      <c r="C27" s="9">
+        <v>30</v>
+      </c>
+      <c r="D27" s="9">
+        <v>10</v>
+      </c>
+      <c r="E27" s="9">
+        <v>30</v>
+      </c>
+      <c r="F27" s="9">
+        <v>0</v>
+      </c>
+      <c r="G27" s="9">
+        <v>0</v>
+      </c>
+      <c r="H27" s="9">
+        <v>200</v>
+      </c>
+      <c r="I27" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="10" t="str">
+        <v>770</v>
+      </c>
+      <c r="J27" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="12"/>
+        <v>670</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="319" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35EB406E-B796-4869-B7ED-61E931538ED9}"/>
+  <xr:revisionPtr revIDLastSave="331" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B31908E6-C082-462D-83E0-43A5857AB76E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="49">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>return home &amp; light revision</t>
+  </si>
+  <si>
+    <t>celebrate ganesh chaturthi</t>
   </si>
 </sst>
 </file>
@@ -1809,27 +1812,51 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="10" t="str">
+    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B28" s="9">
+        <v>420</v>
+      </c>
+      <c r="C28" s="9">
+        <v>45</v>
+      </c>
+      <c r="D28" s="9">
+        <v>120</v>
+      </c>
+      <c r="E28" s="9">
+        <v>90</v>
+      </c>
+      <c r="F28" s="9">
+        <v>150</v>
+      </c>
+      <c r="G28" s="9">
+        <v>3</v>
+      </c>
+      <c r="H28" s="9">
+        <v>250</v>
+      </c>
+      <c r="I28" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="10" t="str">
+        <v>1075</v>
+      </c>
+      <c r="J28" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="12"/>
+        <v>365</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="331" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B31908E6-C082-462D-83E0-43A5857AB76E}"/>
+  <xr:revisionPtr revIDLastSave="343" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C20851CC-6B5E-4C8E-995B-61D6E8F8A1B8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="50">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>celebrate ganesh chaturthi</t>
+  </si>
+  <si>
+    <t>happy</t>
   </si>
 </sst>
 </file>
@@ -1859,26 +1862,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="10" t="str">
+      <c r="A29" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B29" s="9">
+        <v>420</v>
+      </c>
+      <c r="C29" s="9">
+        <v>45</v>
+      </c>
+      <c r="D29" s="9">
+        <v>60</v>
+      </c>
+      <c r="E29" s="9">
+        <v>45</v>
+      </c>
+      <c r="F29" s="9">
+        <v>350</v>
+      </c>
+      <c r="G29" s="9">
+        <v>7</v>
+      </c>
+      <c r="H29" s="9">
+        <v>300</v>
+      </c>
+      <c r="I29" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="10" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J29" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="12"/>
+        <v>220</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N29" s="12" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="343" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C20851CC-6B5E-4C8E-995B-61D6E8F8A1B8}"/>
+  <xr:revisionPtr revIDLastSave="367" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11FB1F29-CB93-4256-89F0-2A2C9037CDDB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="51">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>happy</t>
+  </si>
+  <si>
+    <t>hectic</t>
   </si>
 </sst>
 </file>
@@ -1908,48 +1911,96 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="10" t="str">
+      <c r="A30" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B30" s="9">
+        <v>420</v>
+      </c>
+      <c r="C30" s="9">
+        <v>40</v>
+      </c>
+      <c r="D30" s="9">
+        <v>60</v>
+      </c>
+      <c r="E30" s="9">
+        <v>45</v>
+      </c>
+      <c r="F30" s="9">
+        <v>200</v>
+      </c>
+      <c r="G30" s="9">
+        <v>4</v>
+      </c>
+      <c r="H30" s="9">
+        <v>180</v>
+      </c>
+      <c r="I30" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="10" t="str">
+        <v>945</v>
+      </c>
+      <c r="J30" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="12"/>
+        <v>495</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="10" t="str">
+      <c r="A31" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B31" s="9">
+        <v>420</v>
+      </c>
+      <c r="C31" s="9">
+        <v>60</v>
+      </c>
+      <c r="D31" s="9">
+        <v>90</v>
+      </c>
+      <c r="E31" s="9">
+        <v>45</v>
+      </c>
+      <c r="F31" s="9">
+        <v>350</v>
+      </c>
+      <c r="G31" s="9">
+        <v>7</v>
+      </c>
+      <c r="H31" s="9">
+        <v>180</v>
+      </c>
+      <c r="I31" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="10" t="str">
+        <v>1145</v>
+      </c>
+      <c r="J31" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="12"/>
+        <v>295</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="367" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11FB1F29-CB93-4256-89F0-2A2C9037CDDB}"/>
+  <xr:revisionPtr revIDLastSave="380" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9224CD8-C31F-4C9F-A568-66DE6FF8671F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="51">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -2003,26 +2003,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="10" t="str">
+      <c r="A32" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B32" s="9">
+        <v>420</v>
+      </c>
+      <c r="C32" s="9">
+        <v>30</v>
+      </c>
+      <c r="D32" s="9">
+        <v>60</v>
+      </c>
+      <c r="E32" s="9">
+        <v>40</v>
+      </c>
+      <c r="F32" s="9">
+        <v>300</v>
+      </c>
+      <c r="G32" s="9">
+        <v>6</v>
+      </c>
+      <c r="H32" s="9">
+        <v>200</v>
+      </c>
+      <c r="I32" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="10" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J32" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="12"/>
+        <v>390</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="380" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9224CD8-C31F-4C9F-A568-66DE6FF8671F}"/>
+  <xr:revisionPtr revIDLastSave="395" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD2DCAC9-ADFC-4961-ADE7-A33677E5FDDE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="52">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -189,6 +189,9 @@
   </si>
   <si>
     <t>hectic</t>
+  </si>
+  <si>
+    <t>analytic Ca</t>
   </si>
 </sst>
 </file>
@@ -2049,26 +2052,50 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="10" t="str">
+      <c r="A33" s="8">
+        <v>46284</v>
+      </c>
+      <c r="B33" s="9">
+        <v>420</v>
+      </c>
+      <c r="C33" s="9">
+        <v>45</v>
+      </c>
+      <c r="D33" s="9">
+        <v>90</v>
+      </c>
+      <c r="E33" s="9">
+        <v>60</v>
+      </c>
+      <c r="F33" s="9">
+        <v>150</v>
+      </c>
+      <c r="G33" s="9">
+        <v>2</v>
+      </c>
+      <c r="H33" s="9">
+        <v>200</v>
+      </c>
+      <c r="I33" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="10" t="str">
+        <v>965</v>
+      </c>
+      <c r="J33" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="12"/>
+        <v>475</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N33" s="12" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="395" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD2DCAC9-ADFC-4961-ADE7-A33677E5FDDE}"/>
+  <xr:revisionPtr revIDLastSave="410" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22C5E7B0-5C5F-4408-93C5-24155E4ACAC1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="53">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>analytic Ca</t>
+  </si>
+  <si>
+    <t>recovery mode</t>
   </si>
 </sst>
 </file>
@@ -2098,26 +2101,50 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="10" t="str">
+      <c r="A34" s="8">
+        <v>46285</v>
+      </c>
+      <c r="B34" s="9">
+        <v>480</v>
+      </c>
+      <c r="C34" s="9">
+        <v>40</v>
+      </c>
+      <c r="D34" s="9">
+        <v>120</v>
+      </c>
+      <c r="E34" s="9">
+        <v>60</v>
+      </c>
+      <c r="F34" s="9">
+        <v>0</v>
+      </c>
+      <c r="G34" s="9">
+        <v>0</v>
+      </c>
+      <c r="H34" s="9">
+        <v>250</v>
+      </c>
+      <c r="I34" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="10" t="str">
+        <v>950</v>
+      </c>
+      <c r="J34" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="12"/>
+        <v>490</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="8"/>

--- a/12613356.xlsx
+++ b/12613356.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0c5ea7b5c0f020d/Desktop/CAP 776/CAP-776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="410" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22C5E7B0-5C5F-4408-93C5-24155E4ACAC1}"/>
+  <xr:revisionPtr revIDLastSave="423" documentId="8_{7FDAD421-8814-4830-A1D8-C9C2A23F8EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B81921E-1EE4-4054-9944-4EB898B7322E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12348" xr2:uid="{24114507-0DC2-48E7-A782-B3DFA67E219B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="53">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -2147,26 +2147,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="10" t="str">
+      <c r="A35" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B35" s="9">
+        <v>420</v>
+      </c>
+      <c r="C35" s="9">
+        <v>50</v>
+      </c>
+      <c r="D35" s="9">
+        <v>60</v>
+      </c>
+      <c r="E35" s="9">
+        <v>90</v>
+      </c>
+      <c r="F35" s="9">
+        <v>150</v>
+      </c>
+      <c r="G35" s="9">
+        <v>3</v>
+      </c>
+      <c r="H35" s="9">
+        <v>200</v>
+      </c>
+      <c r="I35" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="10" t="str">
+        <v>970</v>
+      </c>
+      <c r="J35" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="12"/>
+        <v>470</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>
